--- a/artfynd/S 2707-2026 artfynd.xlsx
+++ b/artfynd/S 2707-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ43"/>
+  <dimension ref="A1:AZ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2201,10 +2201,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>720346</v>
+        <v>137451595</v>
       </c>
       <c r="B15" t="n">
-        <v>96231</v>
+        <v>96734</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2212,34 +2212,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Floda, träd 15439 (ek), Vg</t>
+          <t>Brunnslyckan, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>346195</v>
+        <v>346224</v>
       </c>
       <c r="R15" t="n">
-        <v>6410517</v>
+        <v>6410716</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2266,12 +2270,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2006-04-21</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2006-04-21</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,42 +2284,31 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>1 substratenheter # ek</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lars Sjögren</t>
+          <t>Johan Ennerfelt</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Gunnar Flygh</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Epifyt-inv. Särskilt skyddsvärda träd 2005-2007</t>
-        </is>
-      </c>
+          <t>Johan Ennerfelt</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/720346</t>
+          <t>https://artportalen.se/Sighting/137451595</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>720350</v>
+        <v>720346</v>
       </c>
       <c r="B16" t="n">
         <v>96231</v>
@@ -2346,14 +2339,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Floda, träd 15455 (ek), Vg</t>
+          <t>Floda, träd 15439 (ek), Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>346247</v>
+        <v>346195</v>
       </c>
       <c r="R16" t="n">
-        <v>6410132</v>
+        <v>6410517</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2423,13 +2416,13 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/720350</t>
+          <t>https://artportalen.se/Sighting/720346</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>720351</v>
+        <v>720350</v>
       </c>
       <c r="B17" t="n">
         <v>96231</v>
@@ -2460,14 +2453,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Floda, träd 15456 (ek), Vg</t>
+          <t>Floda, träd 15455 (ek), Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>346249</v>
+        <v>346247</v>
       </c>
       <c r="R17" t="n">
-        <v>6410157</v>
+        <v>6410132</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2537,13 +2530,13 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/720351</t>
+          <t>https://artportalen.se/Sighting/720350</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>720352</v>
+        <v>720351</v>
       </c>
       <c r="B18" t="n">
         <v>96231</v>
@@ -2574,14 +2567,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Floda, träd 15436 (ek), Vg</t>
+          <t>Floda, träd 15456 (ek), Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>346195</v>
+        <v>346249</v>
       </c>
       <c r="R18" t="n">
-        <v>6410679</v>
+        <v>6410157</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2651,13 +2644,13 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/720352</t>
+          <t>https://artportalen.se/Sighting/720351</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>720353</v>
+        <v>720352</v>
       </c>
       <c r="B19" t="n">
         <v>96231</v>
@@ -2688,14 +2681,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Floda, träd 15437 (ek), Vg</t>
+          <t>Floda, träd 15436 (ek), Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>346232</v>
+        <v>346195</v>
       </c>
       <c r="R19" t="n">
-        <v>6410547</v>
+        <v>6410679</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2765,13 +2758,13 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/720353</t>
+          <t>https://artportalen.se/Sighting/720352</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>720657</v>
+        <v>720353</v>
       </c>
       <c r="B20" t="n">
         <v>96231</v>
@@ -2802,14 +2795,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kvikulla, träd 15432 (ek), Vg</t>
+          <t>Floda, träd 15437 (ek), Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>346211</v>
+        <v>346232</v>
       </c>
       <c r="R20" t="n">
-        <v>6410559</v>
+        <v>6410547</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2879,16 +2872,16 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/720657</t>
+          <t>https://artportalen.se/Sighting/720353</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>93817209</v>
+        <v>720657</v>
       </c>
       <c r="B21" t="n">
-        <v>96348</v>
+        <v>96231</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2896,37 +2889,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2810</v>
+        <v>2779</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kvikullavägen, Vg</t>
+          <t>Kvikulla, träd 15432 (ek), Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>346196</v>
+        <v>346211</v>
       </c>
       <c r="R21" t="n">
-        <v>6410740</v>
+        <v>6410559</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2950,12 +2943,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2018-06-19</t>
+          <t>2006-04-21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2018-06-19</t>
+          <t>2006-04-21</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2966,28 +2959,40 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>1 substratenheter # ek</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Tage Vowles</t>
+          <t>Lars Sjögren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tage Vowles</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Gunnar Flygh</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Epifyt-inv. Särskilt skyddsvärda träd 2005-2007</t>
+        </is>
+      </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/93817209</t>
+          <t>https://artportalen.se/Sighting/720657</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>107395820</v>
+        <v>93817209</v>
       </c>
       <c r="B22" t="n">
         <v>96348</v>
@@ -3018,17 +3023,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tollered, Vg</t>
+          <t>Kvikullavägen, Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>346191</v>
+        <v>346196</v>
       </c>
       <c r="R22" t="n">
-        <v>6410735</v>
+        <v>6410740</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3052,12 +3057,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2018-06-19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2018-06-19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3072,75 +3077,65 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Tage Vowles</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Rasmus Andgren Ullberg</t>
+          <t>Tage Vowles</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107395820</t>
+          <t>https://artportalen.se/Sighting/93817209</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>16955312</v>
+        <v>107395820</v>
       </c>
       <c r="B23" t="n">
-        <v>91867</v>
+        <v>96348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5445</v>
+        <v>2810</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kvikullavägen, Vg</t>
+          <t>Tollered, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>346170</v>
+        <v>346191</v>
       </c>
       <c r="R23" t="n">
-        <v>6410688</v>
+        <v>6410735</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3164,12 +3159,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2014-11-13</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2014-11-13</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3178,72 +3173,81 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anita Sjöstrand</t>
+          <t>Tim Hipkiss</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anita Sjöstrand</t>
+          <t>Rasmus Andgren Ullberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16955312</t>
+          <t>https://artportalen.se/Sighting/107395820</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2372655</v>
+        <v>16955312</v>
       </c>
       <c r="B24" t="n">
-        <v>78728</v>
+        <v>91867</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6436</v>
+        <v>5445</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gulpudrad spiklav</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Calicium adspersum</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Pers.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Floda, träd 15450 (ek), Vg</t>
+          <t>Kvikullavägen, Vg</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>346211</v>
+        <v>346170</v>
       </c>
       <c r="R24" t="n">
-        <v>6410274</v>
+        <v>6410688</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3267,12 +3271,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2006-04-21</t>
+          <t>2014-11-13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2006-04-21</t>
+          <t>2014-11-13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3281,42 +3285,31 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>1 substratenheter # ek</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lars Sjögren</t>
+          <t>Anita Sjöstrand</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Gunnar Flygh</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Epifyt-inv. Särskilt skyddsvärda träd 2005-2007</t>
-        </is>
-      </c>
+          <t>Anita Sjöstrand</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2372655</t>
+          <t>https://artportalen.se/Sighting/16955312</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2372656</v>
+        <v>2372655</v>
       </c>
       <c r="B25" t="n">
         <v>78728</v>
@@ -3347,14 +3340,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Floda, träd 15447 (ek), Vg</t>
+          <t>Floda, träd 15450 (ek), Vg</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>346296</v>
+        <v>346211</v>
       </c>
       <c r="R25" t="n">
-        <v>6410323</v>
+        <v>6410274</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3424,13 +3417,13 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2372656</t>
+          <t>https://artportalen.se/Sighting/2372655</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2372657</v>
+        <v>2372656</v>
       </c>
       <c r="B26" t="n">
         <v>78728</v>
@@ -3461,14 +3454,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Floda, träd 15445 (ek), Vg</t>
+          <t>Floda, träd 15447 (ek), Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>346305</v>
+        <v>346296</v>
       </c>
       <c r="R26" t="n">
-        <v>6410268</v>
+        <v>6410323</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3538,16 +3531,16 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2372657</t>
+          <t>https://artportalen.se/Sighting/2372656</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>116996490</v>
+        <v>2372657</v>
       </c>
       <c r="B27" t="n">
-        <v>57258</v>
+        <v>78728</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3555,49 +3548,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100065</v>
+        <v>6436</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Calicium adspersum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Damm 5, Stålebodalen, Vg</t>
+          <t>Floda, träd 15445 (ek), Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>346204</v>
+        <v>346305</v>
       </c>
       <c r="R27" t="n">
-        <v>6410404</v>
+        <v>6410268</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3621,22 +3602,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2006-04-21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>10:20</t>
+          <t>2006-04-21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3647,48 +3618,60 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>1 substratenheter # ek</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Hans Falklind</t>
+          <t>Lars Sjögren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Hans Falklind</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Gunnar Flygh</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Epifyt-inv. Särskilt skyddsvärda träd 2005-2007</t>
+        </is>
+      </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116996490</t>
+          <t>https://artportalen.se/Sighting/2372657</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>100609154</v>
+        <v>116996490</v>
       </c>
       <c r="B28" t="n">
-        <v>58203</v>
+        <v>57258</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100124</v>
+        <v>100065</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Backsvala</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Riparia riparia</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3696,23 +3679,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lerum, Vg</t>
+          <t>Damm 5, Stålebodalen, Vg</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>346309</v>
+        <v>346204</v>
       </c>
       <c r="R28" t="n">
-        <v>6410278</v>
+        <v>6410404</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3736,22 +3728,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-05-08</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-05-08</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3766,77 +3758,68 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Carl Simonsson</t>
+          <t>Hans Falklind</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Carl Simonsson</t>
+          <t>Hans Falklind</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100609154</t>
+          <t>https://artportalen.se/Sighting/116996490</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>69117467</v>
+        <v>100609154</v>
       </c>
       <c r="B29" t="n">
-        <v>12646</v>
+        <v>58203</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100236</v>
+        <v>100124</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gulbent kamklobagge</t>
+          <t>Backsvala</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Allecula morio</t>
+          <t>Riparia riparia</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>fönsterfälla</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stålebo, Vg</t>
+          <t>Lerum, Vg</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>346115</v>
+        <v>346309</v>
       </c>
       <c r="R29" t="n">
-        <v>6410583</v>
+        <v>6410278</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3860,12 +3843,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2017-06-14</t>
+          <t>2022-05-08</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2017-07-13</t>
+          <t>2022-05-08</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3877,85 +3870,65 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Lövskog klass 2, NB</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>ek</t>
-        </is>
-      </c>
-      <c r="AS29" t="inlineStr">
-        <is>
-          <t>Niklas Franc</t>
-        </is>
-      </c>
-      <c r="AT29" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
+      <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Peter  Post</t>
+          <t>Carl Simonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Peter  Post</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Insektsinventeringar i Västra Götalands län - Länsstyrelsen</t>
-        </is>
-      </c>
+          <t>Carl Simonsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69117467</t>
+          <t>https://artportalen.se/Sighting/100609154</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>73344868</v>
+        <v>69117467</v>
       </c>
       <c r="B30" t="n">
-        <v>9596</v>
+        <v>12646</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>101479</v>
+        <v>100236</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Läderbagge</t>
+          <t>Gulbent kamklobagge</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Osmoderma eremita</t>
+          <t>Allecula morio</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fönsterfälla</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3964,10 +3937,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>346225</v>
+        <v>346115</v>
       </c>
       <c r="R30" t="n">
-        <v>6410600</v>
+        <v>6410583</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3994,17 +3967,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2017-07-01</t>
+          <t>2017-06-14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2017-07-01</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre spillning i hålek.Trädet trängs av uppväxande bok och bör friställas.</t>
+          <t>2017-07-13</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4013,11 +3981,29 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AT30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Lövskog klass 2, NB</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>ek</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>Niklas Franc</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
       <c r="AW30" t="inlineStr">
         <is>
           <t>Peter  Post</t>
@@ -4030,56 +4016,53 @@
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>Åtgärdsprogram för skalbaggar i eklågor i Västra Götalands län</t>
+          <t>Insektsinventeringar i Västra Götalands län - Länsstyrelsen</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73344868</t>
+          <t>https://artportalen.se/Sighting/69117467</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>69117481</v>
+        <v>73344868</v>
       </c>
       <c r="B31" t="n">
-        <v>12215</v>
+        <v>9596</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102152</v>
+        <v>101479</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Aspögonbagge</t>
+          <t>Läderbagge</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Aderus populneus</t>
+          <t>Osmoderma eremita</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Creutzer, 1796)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>fönsterfälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4088,10 +4071,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>346202</v>
+        <v>346225</v>
       </c>
       <c r="R31" t="n">
-        <v>6410483</v>
+        <v>6410600</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4118,12 +4101,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2017-07-13</t>
+          <t>2017-07-01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2017-08-23</t>
+          <t>2017-07-01</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre spillning i hålek.Trädet trängs av uppväxande bok och bör friställas.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4132,39 +4120,11 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Lövskog klass 2, NB</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>ek</t>
-        </is>
-      </c>
-      <c r="AQ31" t="inlineStr">
-        <is>
-          <t>Niklas Franc</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>NF17061</t>
-        </is>
-      </c>
-      <c r="AS31" t="inlineStr">
-        <is>
-          <t>Niklas Franc</t>
-        </is>
-      </c>
-      <c r="AT31" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
+      <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
           <t>Peter  Post</t>
@@ -4177,21 +4137,21 @@
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>Insektsinventeringar i Västra Götalands län - Länsstyrelsen</t>
+          <t>Åtgärdsprogram för skalbaggar i eklågor i Västra Götalands län</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69117481</t>
+          <t>https://artportalen.se/Sighting/73344868</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>100609175</v>
+        <v>69117481</v>
       </c>
       <c r="B32" t="n">
-        <v>57105</v>
+        <v>12215</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4199,40 +4159,49 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102932</v>
+        <v>102152</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Aspögonbagge</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Aderus populneus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Creutzer, 1796)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>fönsterfälla</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lerum, Vg</t>
+          <t>Stålebo, Vg</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>346309</v>
+        <v>346202</v>
       </c>
       <c r="R32" t="n">
-        <v>6410278</v>
+        <v>6410483</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4256,22 +4225,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-05-08</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:29</t>
+          <t>2017-07-13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-05-08</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>10:29</t>
+          <t>2017-08-23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4283,27 +4242,60 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
-      <c r="AT32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Lövskog klass 2, NB</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>ek</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>Niklas Franc</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>NF17061</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>Niklas Franc</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Carl Simonsson</t>
+          <t>Peter  Post</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Carl Simonsson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Peter  Post</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Insektsinventeringar i Västra Götalands län - Länsstyrelsen</t>
+        </is>
+      </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100609175</t>
+          <t>https://artportalen.se/Sighting/69117481</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123612718</v>
+        <v>100609175</v>
       </c>
       <c r="B33" t="n">
         <v>57105</v>
@@ -4331,32 +4323,23 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Damm 5, Stålebodalen, Vg</t>
+          <t>Lerum, Vg</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>346204</v>
+        <v>346309</v>
       </c>
       <c r="R33" t="n">
-        <v>6410404</v>
+        <v>6410278</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4380,22 +4363,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2022-05-08</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2022-05-08</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4410,27 +4393,27 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Hans Falklind</t>
+          <t>Carl Simonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Hans Falklind</t>
+          <t>Carl Simonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123612718</t>
+          <t>https://artportalen.se/Sighting/100609175</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>116996472</v>
+        <v>123612718</v>
       </c>
       <c r="B34" t="n">
-        <v>58209</v>
+        <v>57105</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4438,16 +4421,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102980</v>
+        <v>102932</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4457,7 +4440,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -4504,22 +4487,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4545,16 +4528,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116996472</t>
+          <t>https://artportalen.se/Sighting/123612718</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117356296</v>
+        <v>116996472</v>
       </c>
       <c r="B35" t="n">
-        <v>58541</v>
+        <v>58209</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4562,16 +4545,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102987</v>
+        <v>102980</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Motacilla alba</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4581,27 +4564,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Parkeringen, Stålebodalen, Vg</t>
+          <t>Damm 5, Stålebodalen, Vg</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>346218</v>
+        <v>346204</v>
       </c>
       <c r="R35" t="n">
-        <v>6410548</v>
+        <v>6410404</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4628,22 +4611,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4658,80 +4641,77 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Peter Strandvik</t>
+          <t>Hans Falklind</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Peter Strandvik</t>
+          <t>Hans Falklind</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117356296</t>
+          <t>https://artportalen.se/Sighting/116996472</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>65332610</v>
+        <v>117356296</v>
       </c>
       <c r="B36" t="n">
-        <v>58439</v>
+        <v>58541</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103018</v>
+        <v>102987</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Utsikten, Stålebodalen, Vg</t>
+          <t>Parkeringen, Stålebodalen, Vg</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>346259</v>
+        <v>346218</v>
       </c>
       <c r="R36" t="n">
-        <v>6410240</v>
+        <v>6410548</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4755,22 +4735,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2017-05-05</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2017-05-05</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4785,24 +4765,24 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Allan Högberg</t>
+          <t>Peter Strandvik</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Allan Högberg, Eva Elison</t>
+          <t>Peter Strandvik</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/65332610</t>
+          <t>https://artportalen.se/Sighting/117356296</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>100609140</v>
+        <v>65332610</v>
       </c>
       <c r="B37" t="n">
         <v>58439</v>
@@ -4830,20 +4810,32 @@
           <t>(Pallas, 1764)</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lerum, Vg</t>
+          <t>Utsikten, Stålebodalen, Vg</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>346309</v>
+        <v>346259</v>
       </c>
       <c r="R37" t="n">
-        <v>6410278</v>
+        <v>6410240</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4870,22 +4862,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2022-05-08</t>
+          <t>2017-05-05</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2022-05-08</t>
+          <t>2017-05-05</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4900,27 +4892,27 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Carl Simonsson</t>
+          <t>Allan Högberg</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Carl Simonsson</t>
+          <t>Allan Högberg, Eva Elison</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100609140</t>
+          <t>https://artportalen.se/Sighting/65332610</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132965739</v>
+        <v>100609140</v>
       </c>
       <c r="B38" t="n">
-        <v>58461</v>
+        <v>58439</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4945,36 +4937,23 @@
           <t>(Pallas, 1764)</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Damm 5, Stålebodalen, Vg</t>
+          <t>Lerum, Vg</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>346204</v>
+        <v>346309</v>
       </c>
       <c r="R38" t="n">
-        <v>6410404</v>
+        <v>6410278</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4998,22 +4977,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2022-05-08</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2022-05-08</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5028,74 +5007,78 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Hans Falklind</t>
+          <t>Carl Simonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Hans Falklind</t>
+          <t>Carl Simonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132965739</t>
+          <t>https://artportalen.se/Sighting/100609140</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117151699</v>
+        <v>132965739</v>
       </c>
       <c r="B39" t="n">
-        <v>58353</v>
+        <v>58461</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103037</v>
+        <v>103018</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Parkeringen, Stålebodalen, Vg</t>
+          <t>Damm 5, Stålebodalen, Vg</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>346218</v>
+        <v>346204</v>
       </c>
       <c r="R39" t="n">
-        <v>6410548</v>
+        <v>6410404</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -5122,22 +5105,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5152,27 +5135,27 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Peter Strandvik</t>
+          <t>Hans Falklind</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Peter Strandvik</t>
+          <t>Hans Falklind</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117151699</t>
+          <t>https://artportalen.se/Sighting/132965739</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117524152</v>
+        <v>117151699</v>
       </c>
       <c r="B40" t="n">
-        <v>58602</v>
+        <v>58353</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5180,33 +5163,33 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103042</v>
+        <v>103037</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5246,22 +5229,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5287,33 +5270,38 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117524152</t>
+          <t>https://artportalen.se/Sighting/117151699</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>69116707</v>
+        <v>117524152</v>
       </c>
       <c r="B41" t="n">
-        <v>4812</v>
+        <v>58602</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>105332</v>
+        <v>103042</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dorcatoma chrysomelina</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Sturm, 1837</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5321,27 +5309,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>fönsterfälla</t>
-        </is>
-      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stålebo, Vg</t>
+          <t>Parkeringen, Stålebodalen, Vg</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>346202</v>
+        <v>346218</v>
       </c>
       <c r="R41" t="n">
-        <v>6410483</v>
+        <v>6410548</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5365,12 +5353,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2017-06-14</t>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2017-07-13</t>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5382,53 +5380,30 @@
       <c r="AG41" t="b">
         <v>0</v>
       </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Lövskog klass 2, NB</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>ek</t>
-        </is>
-      </c>
-      <c r="AS41" t="inlineStr">
-        <is>
-          <t>Niklas Franc</t>
-        </is>
-      </c>
-      <c r="AT41" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
+      <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Peter  Post</t>
+          <t>Peter Strandvik</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Peter  Post</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>Insektsinventeringar i Västra Götalands län - Länsstyrelsen</t>
-        </is>
-      </c>
+          <t>Peter Strandvik</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69116707</t>
+          <t>https://artportalen.se/Sighting/117524152</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117524145</v>
+        <v>69116707</v>
       </c>
       <c r="B42" t="n">
-        <v>58085</v>
+        <v>4812</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5436,21 +5411,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>205976</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Gråkråka</t>
-        </is>
+        <v>105332</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Dorcatoma chrysomelina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sturm, 1837</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5458,27 +5428,27 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>fönsterfälla</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Parkeringen, Stålebodalen, Vg</t>
+          <t>Stålebo, Vg</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>346218</v>
+        <v>346202</v>
       </c>
       <c r="R42" t="n">
-        <v>6410548</v>
+        <v>6410483</v>
       </c>
       <c r="S42" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5502,22 +5472,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>10:15</t>
+          <t>2017-06-14</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>11:25</t>
+          <t>2017-07-13</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5529,30 +5489,53 @@
       <c r="AG42" t="b">
         <v>0</v>
       </c>
-      <c r="AT42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Lövskog klass 2, NB</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>ek</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
+          <t>Niklas Franc</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Peter Strandvik</t>
+          <t>Peter  Post</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Peter Strandvik</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
+          <t>Peter  Post</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Insektsinventeringar i Västra Götalands län - Länsstyrelsen</t>
+        </is>
+      </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117524145</t>
+          <t>https://artportalen.se/Sighting/69116707</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>55926149</v>
+        <v>117524145</v>
       </c>
       <c r="B43" t="n">
-        <v>101326</v>
+        <v>58085</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5560,52 +5543,49 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>205976</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Utsikten, Stålebodalen, Vg</t>
+          <t>Parkeringen, Stålebodalen, Vg</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>346259</v>
+        <v>346218</v>
       </c>
       <c r="R43" t="n">
-        <v>6410240</v>
+        <v>6410548</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5629,22 +5609,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2008-03-31</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2008-03-31</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5659,16 +5639,143 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Allan Högberg</t>
+          <t>Peter Strandvik</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Allan Högberg, Eva Elison</t>
+          <t>Peter Strandvik</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117524145</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>55926149</v>
+      </c>
+      <c r="B44" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Utsikten, Stålebodalen, Vg</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>346259</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6410240</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Skallsjö</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2008-03-31</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2008-03-31</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Allan Högberg</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Allan Högberg, Eva Elison</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/55926149</t>
         </is>
@@ -5718,6 +5825,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 2707-2026 artfynd.xlsx
+++ b/artfynd/S 2707-2026 artfynd.xlsx
@@ -2204,7 +2204,7 @@
         <v>137451595</v>
       </c>
       <c r="B15" t="n">
-        <v>96734</v>
+        <v>96737</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/S 2707-2026 artfynd.xlsx
+++ b/artfynd/S 2707-2026 artfynd.xlsx
@@ -2204,7 +2204,7 @@
         <v>137451595</v>
       </c>
       <c r="B15" t="n">
-        <v>96737</v>
+        <v>96741</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
